--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$67</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2316" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1118,10 +1121,67 @@
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:extension.value}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Request.occurrence[x]</t>
   </si>
   <si>
     <t>see dosageInstruction mapping</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:otherDosage</t>
+  </si>
+  <si>
+    <t>otherDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-other-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:timedDosage</t>
+  </si>
+  <si>
+    <t>timedDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-timed-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:frequencyDosage</t>
+  </si>
+  <si>
+    <t>frequencyDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-frequency-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:freitextDosage</t>
+  </si>
+  <si>
+    <t>freitextDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-freetext-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:standardDosage</t>
+  </si>
+  <si>
+    <t>standardDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-standard-administration}
+</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest</t>
@@ -1621,6 +1681,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1802,12 +1877,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO62"/>
+  <dimension ref="A1:AO67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.73046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1972,7 +2047,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2087,7 +2162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2204,7 +2279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -2319,7 +2394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>103</v>
       </c>
@@ -2436,7 +2511,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>109</v>
       </c>
@@ -2553,7 +2628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -2670,7 +2745,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2787,7 +2862,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -2904,7 +2979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
@@ -3023,7 +3098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>147</v>
       </c>
@@ -3140,7 +3215,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -3257,7 +3332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>168</v>
       </c>
@@ -3374,7 +3449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>178</v>
       </c>
@@ -3491,7 +3566,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>187</v>
       </c>
@@ -3608,7 +3683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>195</v>
       </c>
@@ -3723,7 +3798,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>203</v>
       </c>
@@ -3840,7 +3915,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>209</v>
       </c>
@@ -3955,7 +4030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>214</v>
       </c>
@@ -4072,7 +4147,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>226</v>
       </c>
@@ -4189,7 +4264,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>236</v>
       </c>
@@ -4306,7 +4381,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>245</v>
       </c>
@@ -4421,7 +4496,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>251</v>
       </c>
@@ -4536,7 +4611,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>260</v>
       </c>
@@ -4651,7 +4726,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>266</v>
       </c>
@@ -4766,7 +4841,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>273</v>
       </c>
@@ -4883,7 +4958,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>281</v>
       </c>
@@ -4998,7 +5073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>287</v>
       </c>
@@ -5115,7 +5190,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>298</v>
       </c>
@@ -5232,7 +5307,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>305</v>
       </c>
@@ -5347,7 +5422,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>311</v>
       </c>
@@ -5462,7 +5537,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>314</v>
       </c>
@@ -5577,7 +5652,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>320</v>
       </c>
@@ -5694,7 +5769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>326</v>
       </c>
@@ -5811,7 +5886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>333</v>
       </c>
@@ -5926,7 +6001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>339</v>
       </c>
@@ -6041,7 +6116,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>346</v>
       </c>
@@ -6054,13 +6129,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -6116,16 +6191,14 @@
         <v>21</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>346</v>
@@ -6143,13 +6216,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
@@ -6160,12 +6233,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6174,10 +6249,10 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6186,15 +6261,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6243,13 +6320,13 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -6258,13 +6335,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6275,12 +6352,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="B39" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6289,10 +6368,10 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6304,12 +6383,14 @@
         <v>360</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6358,28 +6439,28 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6390,14 +6471,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="D40" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6407,7 +6490,7 @@
         <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6416,16 +6499,16 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>136</v>
+        <v>363</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>137</v>
+        <v>348</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>139</v>
+        <v>350</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6475,7 +6558,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6487,16 +6570,16 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6507,14 +6590,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="D41" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6524,29 +6609,27 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>136</v>
+        <v>366</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6594,7 +6677,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6606,16 +6689,16 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>133</v>
+        <v>354</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6626,12 +6709,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6640,10 +6725,10 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6652,16 +6737,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6711,13 +6796,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -6726,13 +6811,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6741,12 +6826,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6769,13 +6854,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6826,7 +6911,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6838,16 +6923,16 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -6856,23 +6941,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6884,17 +6969,15 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>137</v>
+        <v>378</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6943,19 +7026,19 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -6964,7 +7047,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -6973,16 +7056,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>369</v>
+        <v>135</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6995,26 +7078,24 @@
         <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>137</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="O45" t="s" s="2">
-        <v>145</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7062,7 +7143,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7083,7 +7164,7 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>133</v>
+        <v>381</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7092,44 +7173,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>382</v>
+        <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7177,19 +7262,19 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
@@ -7198,7 +7283,7 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>385</v>
+        <v>133</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7207,12 +7292,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7235,15 +7320,17 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7292,7 +7379,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7313,7 +7400,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7322,12 +7409,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7350,13 +7437,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7407,7 +7494,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7419,7 +7506,7 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
@@ -7428,7 +7515,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7437,23 +7524,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7465,20 +7552,18 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>395</v>
+        <v>136</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>396</v>
+        <v>137</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7526,28 +7611,28 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>400</v>
+        <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7556,46 +7641,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>403</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7643,42 +7730,42 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>407</v>
+        <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>408</v>
+        <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7701,13 +7788,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7758,7 +7845,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7776,24 +7863,24 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>413</v>
+        <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>415</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7816,17 +7903,15 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7875,7 +7960,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7893,10 +7978,10 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>420</v>
+        <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -7905,12 +7990,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7933,13 +8018,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7990,7 +8075,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8011,21 +8096,21 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8048,16 +8133,20 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8105,7 +8194,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8123,10 +8212,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8135,12 +8224,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8163,15 +8252,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8220,7 +8311,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>419</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8232,41 +8323,41 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>364</v>
+        <v>425</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -8278,17 +8369,15 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>136</v>
+        <v>399</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>137</v>
+        <v>428</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8337,78 +8426,76 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>364</v>
+        <v>431</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>370</v>
+        <v>434</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>371</v>
+        <v>435</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8456,28 +8543,28 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>372</v>
+        <v>433</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>21</v>
+        <v>437</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>133</v>
+        <v>438</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8486,12 +8573,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8499,7 +8586,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>90</v>
@@ -8514,17 +8601,15 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8549,13 +8634,13 @@
         <v>21</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>440</v>
+        <v>21</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
@@ -8573,10 +8658,10 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>90</v>
@@ -8591,19 +8676,19 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>444</v>
       </c>
@@ -8631,7 +8716,7 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>169</v>
+        <v>371</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>445</v>
@@ -8664,13 +8749,13 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>447</v>
+        <v>21</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -8706,24 +8791,24 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AM59" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8746,13 +8831,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>453</v>
+        <v>377</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>454</v>
+        <v>378</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>455</v>
+        <v>379</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8803,7 +8888,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>452</v>
+        <v>380</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8815,16 +8900,16 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>456</v>
+        <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>457</v>
+        <v>381</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8833,16 +8918,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>459</v>
+        <v>135</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8861,16 +8946,16 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>460</v>
+        <v>136</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>137</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
+        <v>383</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>463</v>
+        <v>139</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8920,7 +9005,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>458</v>
+        <v>384</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8932,7 +9017,7 @@
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
@@ -8941,7 +9026,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>464</v>
+        <v>381</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -8950,16 +9035,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8972,24 +9057,26 @@
         <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>466</v>
+        <v>136</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>467</v>
+        <v>387</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>468</v>
+        <v>388</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9037,7 +9124,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>465</v>
+        <v>389</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9049,25 +9136,624 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK62" t="s" s="2">
+      <c r="AK63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K65" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AL62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM62" t="s" s="2">
+      <c r="L65" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AN62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO62" t="s" s="2">
+      <c r="M65" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO67">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI66">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1184,6 +1184,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+frequencySameAsWhenCount:wenn .when verwendet wird und periodUnit = d muss die frequency mit der Anzahl an entries in .when übereinstimmen {(timing.repeat.when.exists() and timing.repeat.periodUnit = 'd') implies timing.repeat.when.distinct().count() = timing.repeat.frequency}weekdaysRequireWeeklyPeriod:DayOfWeek kann nur dann verwendet werden, wenn periodUnit 'wk' ist. {timing.repeat.dayOfWeek.exists() implies timing.repeat.periodUnit = 'wk'}frequencyEqualsEventWeekdayProduct:Wenn Wochentage angegeben sind dann entspricht die frequency dem Produkt aus Wochentagen und der Anzahl an ausgewählten Tageszeiten. {timing.repeat.when.exists() and timing.repeat.dayOfWeek.exists() implies timing.repeat.frequency = timing.repeat.when.distinct().count() * timing.repeat.dayOfWeek.distinct().count()}noDuplicateWhen:Tageszeiten können nicht mehrmals vorkommen. {timing.repeat.when.count() = timing.repeat.when.distinct().count()}noDuplicateDayOfWeek:Wochentage können nicht mehrmals vorkommen. {timing.repeat.dayOfWeek.count() = timing.repeat.dayOfWeek.distinct().count()}allowedPeriodUnitsForStandardAdministration:Für Standarddosierungen im Tageszeitenschema sind nur tägliche, wöchentliche oder monatliche Wiederholungen zulässig. {timing.repeat.periodUnit = 'd' or timing.repeat.periodUnit = 'wk' or timing.repeat.periodUnit = 'm'}</t>
+  </si>
+  <si>
     <t>MedicationRequest.dispenseRequest</t>
   </si>
   <si>
@@ -1283,6 +1287,10 @@
   </si>
   <si>
     <t>The amount or quantity to provide as part of the first dispense.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>Supply.quantity[moodCode=RQO]</t>
@@ -6808,7 +6816,7 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>370</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>353</v>
@@ -6828,10 +6836,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6854,13 +6862,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6911,7 +6919,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6929,10 +6937,10 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -6943,10 +6951,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6969,13 +6977,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7026,7 +7034,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7047,7 +7055,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7058,10 +7066,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7090,7 +7098,7 @@
         <v>137</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>139</v>
@@ -7143,7 +7151,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7164,7 +7172,7 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7175,14 +7183,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7204,10 +7212,10 @@
         <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7262,7 +7270,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7294,10 +7302,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7320,16 +7328,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7379,7 +7387,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7400,7 +7408,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7411,10 +7419,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7437,13 +7445,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7494,7 +7502,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7515,7 +7523,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7526,10 +7534,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7558,7 +7566,7 @@
         <v>137</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>139</v>
@@ -7611,7 +7619,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7632,7 +7640,7 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7643,14 +7651,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7672,10 +7680,10 @@
         <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>139</v>
@@ -7730,7 +7738,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7762,10 +7770,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7788,13 +7796,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7845,7 +7853,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7857,7 +7865,7 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>403</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
@@ -7866,7 +7874,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7877,10 +7885,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7903,13 +7911,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7960,7 +7968,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7981,7 +7989,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -7992,10 +8000,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8018,13 +8026,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8075,7 +8083,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8096,7 +8104,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8107,10 +8115,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8133,19 +8141,19 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8194,7 +8202,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8212,10 +8220,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8226,10 +8234,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8252,16 +8260,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8311,7 +8319,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8329,24 +8337,24 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8369,13 +8377,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8426,7 +8434,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8438,30 +8446,30 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>403</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8484,16 +8492,16 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8543,7 +8551,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8561,10 +8569,10 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8575,10 +8583,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8601,13 +8609,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8658,7 +8666,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8679,7 +8687,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>286</v>
@@ -8690,10 +8698,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8716,13 +8724,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8773,7 +8781,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8791,10 +8799,10 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8805,10 +8813,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8831,13 +8839,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8888,7 +8896,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8909,7 +8917,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8920,10 +8928,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8952,7 +8960,7 @@
         <v>137</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>139</v>
@@ -9005,7 +9013,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9026,7 +9034,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9037,14 +9045,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9066,10 +9074,10 @@
         <v>136</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>139</v>
@@ -9124,7 +9132,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9156,10 +9164,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9182,16 +9190,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9220,10 +9228,10 @@
         <v>173</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9241,7 +9249,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>90</v>
@@ -9259,24 +9267,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9302,10 +9310,10 @@
         <v>169</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9335,10 +9343,10 @@
         <v>173</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9356,7 +9364,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9374,24 +9382,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9414,13 +9422,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9471,7 +9479,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9486,13 +9494,13 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9503,14 +9511,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9529,16 +9537,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9588,7 +9596,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9609,7 +9617,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9620,10 +9628,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9646,16 +9654,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9705,7 +9713,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9720,13 +9728,13 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="549">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -301,7 +301,7 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
+    <t>Technische id der Ressource</t>
   </si>
   <si>
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
@@ -333,14 +333,191 @@
 </t>
   </si>
   <si>
-    <t>MedicationRequest.implicitRules</t>
+    <t>MedicationRequest.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>MedicationRequest.implicitRules</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -406,6 +583,59 @@
     <t>Act.text?</t>
   </si>
   <si>
+    <t>MedicationRequest.text.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.text.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.text.status</t>
+  </si>
+  <si>
+    <t>generated | extensions | additional | empty</t>
+  </si>
+  <si>
+    <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The status of a resource narrative.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/narrative-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Narrative.status</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>MedicationRequest.text.div</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xhtml
+</t>
+  </si>
+  <si>
+    <t>Limited xhtml content</t>
+  </si>
+  <si>
+    <t>The actual narrative content, a stripped down version of XHTML.</t>
+  </si>
+  <si>
+    <t>The contents of the html element are an XHTML fragment containing only the basic html formatting elements described in chapters 7-11 and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained stylesheets. The XHTML content SHALL NOT contain a head, a body, external stylesheet references, scripts, forms, base/link/xlink, frames, iframes and objects.</t>
+  </si>
+  <si>
+    <t>Narrative.div</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+txt-1:The narrative SHALL contain only the basic html formatting elements and attributes described in chapters 7-11 (except section 4 of chapter 9) and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained style attributes {htmlChecks()}txt-2:The narrative SHALL have some non-whitespace content {htmlChecks()}</t>
+  </si>
+  <si>
     <t>MedicationRequest.contained</t>
   </si>
   <si>
@@ -429,34 +659,13 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>MedicationRequest.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -518,9 +727,6 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>A coded concept specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
   </si>
   <si>
@@ -553,9 +759,6 @@
   </si>
   <si>
     <t>This is generally only used for "exception" statuses such as "suspended" or "cancelled". The reason why the MedicationRequest was created at all is captured in reasonCode, not here.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Identifies the reasons for a given status.</t>
@@ -1210,29 +1413,7 @@
     <t>MedicationRequest.dispenseRequest.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationRequest.dispenseRequest.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.modifierExtension</t>
@@ -1885,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO67"/>
+  <dimension ref="A1:AO79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
@@ -1916,7 +2097,7 @@
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2170,7 +2351,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2189,7 +2370,7 @@
         <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>21</v>
@@ -2287,7 +2468,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -2306,7 +2487,7 @@
         <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -2424,10 +2605,10 @@
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>104</v>
@@ -2438,9 +2619,7 @@
       <c r="M5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2489,7 +2668,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2501,7 +2680,7 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -2510,7 +2689,7 @@
         <v>21</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>21</v>
@@ -2528,14 +2707,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2547,16 +2726,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2582,43 +2761,43 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
@@ -2627,7 +2806,7 @@
         <v>21</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>21</v>
@@ -2636,16 +2815,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2655,16 +2834,16 @@
         <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>121</v>
@@ -2744,53 +2923,53 @@
         <v>21</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="AN7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" hidden="true">
-      <c r="A8" t="s" s="2">
-        <v>126</v>
-      </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2840,19 +3019,19 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>21</v>
@@ -2861,7 +3040,7 @@
         <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>21</v>
@@ -2872,21 +3051,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2895,19 +3074,19 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2957,19 +3136,19 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
@@ -2978,7 +3157,7 @@
         <v>21</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>21</v>
@@ -2987,16 +3166,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3006,29 +3185,27 @@
         <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
       </c>
@@ -3076,7 +3253,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3088,7 +3265,7 @@
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -3097,7 +3274,7 @@
         <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>21</v>
@@ -3108,10 +3285,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3131,19 +3308,19 @@
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3169,13 +3346,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -3193,7 +3370,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3208,27 +3385,27 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3236,31 +3413,31 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3286,13 +3463,13 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -3310,13 +3487,13 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
@@ -3325,16 +3502,16 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>21</v>
@@ -3342,10 +3519,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3356,28 +3533,28 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3403,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -3427,7 +3604,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3442,13 +3619,13 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>21</v>
@@ -3459,10 +3636,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3470,7 +3647,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
@@ -3479,22 +3656,22 @@
         <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3520,13 +3697,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3544,10 +3721,10 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>90</v>
@@ -3559,41 +3736,41 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -3602,16 +3779,16 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3637,13 +3814,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3661,13 +3838,13 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -3679,13 +3856,13 @@
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>21</v>
@@ -3693,10 +3870,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3716,16 +3893,16 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>196</v>
+        <v>105</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3752,13 +3929,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3776,7 +3953,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>107</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3788,19 +3965,19 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>201</v>
+        <v>108</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>21</v>
@@ -3808,42 +3985,42 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3881,31 +4058,31 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
@@ -3914,7 +4091,7 @@
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
@@ -3923,12 +4100,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3936,28 +4113,28 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3984,13 +4161,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -4008,10 +4185,10 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>90</v>
@@ -4029,7 +4206,7 @@
         <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
@@ -4038,12 +4215,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4057,25 +4234,25 @@
         <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4101,13 +4278,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -4125,7 +4302,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>90</v>
@@ -4137,41 +4314,41 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>198</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -4180,19 +4357,19 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4242,53 +4419,53 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -4300,16 +4477,16 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>112</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>114</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4359,46 +4536,46 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4411,22 +4588,26 @@
         <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>246</v>
+        <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4474,7 +4655,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4486,19 +4667,19 @@
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>250</v>
+        <v>191</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>21</v>
@@ -4506,10 +4687,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4520,7 +4701,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4529,18 +4710,20 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4589,13 +4772,13 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
@@ -4604,27 +4787,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>259</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4632,7 +4815,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
@@ -4641,21 +4824,23 @@
         <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>261</v>
+        <v>166</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>262</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4680,13 +4865,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>21</v>
+        <v>229</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4704,10 +4889,10 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>90</v>
@@ -4719,16 +4904,16 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>21</v>
@@ -4736,10 +4921,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4762,15 +4947,17 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4795,13 +4982,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4819,7 +5006,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4834,16 +5021,16 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>21</v>
@@ -4851,10 +5038,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4862,7 +5049,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -4871,22 +5058,22 @@
         <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4912,13 +5099,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4936,10 +5123,10 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -4951,16 +5138,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>21</v>
@@ -4968,10 +5155,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4982,7 +5169,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -4994,15 +5181,17 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5027,13 +5216,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5051,13 +5240,13 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
@@ -5069,13 +5258,13 @@
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>21</v>
@@ -5083,10 +5272,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5097,7 +5286,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -5106,20 +5295,18 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5144,13 +5331,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5168,13 +5355,13 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
@@ -5183,27 +5370,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>294</v>
+        <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5214,28 +5401,28 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5285,13 +5472,13 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
@@ -5300,16 +5487,16 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>296</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5317,10 +5504,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5331,7 +5518,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5343,13 +5530,13 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5400,13 +5587,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5415,13 +5602,13 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>309</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>310</v>
+        <v>278</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5432,10 +5619,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5443,10 +5630,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5458,15 +5645,17 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>280</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5491,13 +5680,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>21</v>
+        <v>285</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5515,13 +5704,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5530,27 +5719,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5558,10 +5747,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5573,15 +5762,17 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5630,13 +5821,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -5645,27 +5836,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>21</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5685,21 +5876,21 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>148</v>
+        <v>302</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5747,7 +5938,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5762,27 +5953,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>21</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5793,7 +5984,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -5805,17 +5996,15 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>311</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5840,13 +6029,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5864,13 +6053,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -5879,16 +6068,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>314</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -5896,10 +6085,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5910,7 +6099,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
@@ -5919,16 +6108,16 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5979,13 +6168,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -5994,27 +6183,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>21</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6025,7 +6214,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -6034,16 +6223,16 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6094,13 +6283,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -6109,16 +6298,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6126,10 +6315,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6137,13 +6326,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H37" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -6152,17 +6341,15 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6199,23 +6386,25 @@
         <v>21</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6224,31 +6413,29 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6257,28 +6444,28 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>357</v>
+        <v>235</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6304,13 +6491,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6328,13 +6515,13 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -6343,13 +6530,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6358,16 +6545,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="C39" t="s" s="2">
-        <v>359</v>
-      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6376,10 +6561,10 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6388,7 +6573,7 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>348</v>
@@ -6396,9 +6581,7 @@
       <c r="M39" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6453,7 +6636,7 @@
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6462,31 +6645,29 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6498,7 +6679,7 @@
         <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6507,16 +6688,16 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>363</v>
+        <v>235</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6542,13 +6723,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6566,7 +6747,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6581,31 +6762,29 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>21</v>
+        <v>362</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6617,7 +6796,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6626,16 +6805,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="N41" t="s" s="2">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6685,7 +6864,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6700,31 +6879,29 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6736,26 +6913,24 @@
         <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K42" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6804,7 +6979,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6816,16 +6991,16 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>370</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6836,10 +7011,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6850,7 +7025,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -6859,16 +7034,16 @@
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6919,13 +7094,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -6937,10 +7112,10 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -6951,10 +7126,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6965,7 +7140,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6974,16 +7149,16 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7034,28 +7209,28 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7066,21 +7241,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -7089,21 +7264,21 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>137</v>
+        <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7157,22 +7332,22 @@
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>389</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7183,46 +7358,44 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>136</v>
+        <v>235</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7246,13 +7419,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7270,19 +7443,19 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
@@ -7291,7 +7464,7 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>133</v>
+        <v>397</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7302,10 +7475,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7316,7 +7489,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7328,17 +7501,15 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7387,13 +7558,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7402,13 +7573,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7419,10 +7590,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7433,7 +7604,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7445,13 +7616,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7502,28 +7673,28 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>21</v>
+        <v>409</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7534,24 +7705,24 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7560,16 +7731,16 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>136</v>
+        <v>412</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>137</v>
+        <v>413</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>139</v>
+        <v>415</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7607,19 +7778,17 @@
         <v>21</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>21</v>
+        <v>417</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7631,16 +7800,16 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7649,16 +7818,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="D50" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7668,29 +7839,27 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>136</v>
+        <v>422</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7738,7 +7907,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7750,16 +7919,16 @@
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>133</v>
+        <v>419</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7768,14 +7937,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7784,10 +7955,10 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -7796,15 +7967,17 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7853,28 +8026,28 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>403</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7883,14 +8056,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7899,10 +8074,10 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
@@ -7911,15 +8086,17 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7968,13 +8145,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -7983,13 +8160,13 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -7998,14 +8175,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8014,10 +8193,10 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -8026,15 +8205,17 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8083,13 +8264,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -8098,13 +8279,13 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8113,14 +8294,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8129,10 +8312,10 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -8141,20 +8324,18 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>418</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8202,28 +8383,28 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>435</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8234,10 +8415,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8260,17 +8441,15 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8319,7 +8498,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8337,24 +8516,24 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>428</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8377,13 +8556,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>400</v>
+        <v>104</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>430</v>
+        <v>105</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>431</v>
+        <v>106</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8434,7 +8613,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>429</v>
+        <v>107</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8446,41 +8625,41 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>403</v>
+        <v>21</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>432</v>
+        <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>433</v>
+        <v>108</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>434</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8492,16 +8671,16 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>406</v>
+        <v>111</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>436</v>
+        <v>112</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>437</v>
+        <v>113</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>438</v>
+        <v>114</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8551,28 +8730,28 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>435</v>
+        <v>118</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>440</v>
+        <v>108</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8583,42 +8762,46 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>442</v>
+        <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8666,19 +8849,19 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
@@ -8687,10 +8870,10 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>445</v>
+        <v>191</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -8698,10 +8881,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8724,15 +8907,17 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8781,7 +8966,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8799,10 +8984,10 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8813,10 +8998,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8839,13 +9024,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>378</v>
+        <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>379</v>
+        <v>105</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>380</v>
+        <v>106</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8896,7 +9081,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>381</v>
+        <v>107</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8917,7 +9102,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>382</v>
+        <v>108</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8928,14 +9113,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8954,16 +9139,16 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>384</v>
+        <v>113</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9013,7 +9198,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>385</v>
+        <v>118</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9025,7 +9210,7 @@
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
@@ -9034,7 +9219,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>382</v>
+        <v>108</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9045,14 +9230,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9071,19 +9256,19 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>388</v>
+        <v>446</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>389</v>
+        <v>447</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>145</v>
+        <v>212</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9132,7 +9317,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>390</v>
+        <v>448</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9144,7 +9329,7 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
@@ -9153,7 +9338,7 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9164,10 +9349,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9175,7 +9360,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>90</v>
@@ -9190,17 +9375,15 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9225,13 +9408,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>459</v>
+        <v>21</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>460</v>
+        <v>21</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9249,10 +9432,10 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>90</v>
@@ -9261,22 +9444,22 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>461</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>462</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -9307,13 +9490,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>169</v>
+        <v>464</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9340,13 +9523,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>467</v>
+        <v>21</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9382,24 +9565,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>468</v>
+        <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>470</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9422,13 +9605,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9479,7 +9662,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9494,13 +9677,13 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>468</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9511,21 +9694,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>478</v>
+        <v>21</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -9537,18 +9720,20 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9596,13 +9781,13 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
@@ -9614,10 +9799,10 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>21</v>
+        <v>477</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9628,10 +9813,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9642,7 +9827,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9654,16 +9839,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9713,13 +9898,13 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
@@ -9728,23 +9913,1417 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AN67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO67" t="s" s="2">
+      <c r="AM68" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO79" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO67">
+  <autoFilter ref="A1:AO79">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9754,7 +11333,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI66">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="549">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -671,14 +671,10 @@
     <t>MedicationRequest.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -1428,6 +1424,9 @@
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -3179,10 +3178,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>91</v>
@@ -4575,14 +4574,14 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4602,12 +4601,8 @@
       <c r="M22" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N22" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4655,7 +4650,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4676,7 +4671,7 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4687,10 +4682,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4713,16 +4708,16 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4772,7 +4767,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4787,27 +4782,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4833,13 +4828,13 @@
         <v>166</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4868,11 +4863,11 @@
         <v>187</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>229</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4889,7 +4884,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>90</v>
@@ -4904,16 +4899,16 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>21</v>
@@ -4921,10 +4916,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4947,16 +4942,16 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4985,11 +4980,11 @@
         <v>156</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>240</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
       </c>
@@ -5006,7 +5001,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5021,13 +5016,13 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
@@ -5038,10 +5033,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5067,13 +5062,13 @@
         <v>166</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5102,11 +5097,11 @@
         <v>187</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>248</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
       </c>
@@ -5123,7 +5118,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5138,16 +5133,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>21</v>
@@ -5155,10 +5150,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5181,16 +5176,16 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5219,11 +5214,11 @@
         <v>156</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>257</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
       </c>
@@ -5240,7 +5235,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5258,13 +5253,13 @@
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>259</v>
-      </c>
       <c r="AN27" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>21</v>
@@ -5272,10 +5267,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5301,10 +5296,10 @@
         <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5334,11 +5329,11 @@
         <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5355,7 +5350,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5370,16 +5365,16 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>21</v>
@@ -5387,10 +5382,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5413,16 +5408,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5472,7 +5467,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5493,7 +5488,7 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
@@ -5504,10 +5499,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5530,13 +5525,13 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5587,7 +5582,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5608,7 +5603,7 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5619,10 +5614,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5645,16 +5640,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5683,11 +5678,11 @@
         <v>156</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5704,7 +5699,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>90</v>
@@ -5719,27 +5714,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5762,16 +5757,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5821,7 +5816,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -5836,27 +5831,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5879,16 +5874,16 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5938,7 +5933,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5953,27 +5948,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>309</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5996,13 +5991,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6053,7 +6048,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6068,16 +6063,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>315</v>
-      </c>
       <c r="AN34" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -6085,10 +6080,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6111,13 +6106,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6168,7 +6163,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6183,27 +6178,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6226,13 +6221,13 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6283,7 +6278,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6298,16 +6293,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6315,10 +6310,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6341,13 +6336,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6398,7 +6393,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6413,16 +6408,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6430,10 +6425,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6456,16 +6451,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6494,11 +6489,11 @@
         <v>156</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>343</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6515,7 +6510,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6530,13 +6525,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6547,10 +6542,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6573,13 +6568,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6630,7 +6625,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6651,10 +6646,10 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6662,10 +6657,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6688,16 +6683,16 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6726,11 +6721,11 @@
         <v>156</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6747,7 +6742,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6762,27 +6757,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6805,16 +6800,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6864,7 +6859,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6879,16 +6874,16 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>369</v>
-      </c>
       <c r="AN41" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6896,10 +6891,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6922,13 +6917,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6979,7 +6974,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6994,13 +6989,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -7011,10 +7006,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7040,10 +7035,10 @@
         <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7094,7 +7089,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7115,7 +7110,7 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7126,10 +7121,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7152,13 +7147,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7209,7 +7204,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7224,13 +7219,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7241,10 +7236,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7267,17 +7262,17 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7326,7 +7321,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7341,13 +7336,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7358,10 +7353,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7384,16 +7379,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7422,11 +7417,11 @@
         <v>156</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7443,7 +7438,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7464,7 +7459,7 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7475,10 +7470,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7501,13 +7496,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7558,7 +7553,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7573,13 +7568,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7590,10 +7585,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7616,13 +7611,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7673,7 +7668,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7688,13 +7683,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7705,10 +7700,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7731,16 +7726,16 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7778,17 +7773,17 @@
         <v>21</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7803,13 +7798,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7820,13 +7815,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C50" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>21</v>
@@ -7848,16 +7843,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7907,7 +7902,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7922,13 +7917,13 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7939,13 +7934,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>21</v>
@@ -7967,16 +7962,16 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8026,7 +8021,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8041,13 +8036,13 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8058,13 +8053,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>21</v>
@@ -8086,16 +8081,16 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8145,7 +8140,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8160,13 +8155,13 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8177,13 +8172,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>21</v>
@@ -8205,16 +8200,16 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8264,7 +8259,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8279,13 +8274,13 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8296,13 +8291,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>21</v>
@@ -8324,16 +8319,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8383,7 +8378,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8395,16 +8390,16 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8415,10 +8410,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8441,13 +8436,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8498,7 +8493,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8516,10 +8511,10 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8530,10 +8525,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8645,10 +8640,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8762,14 +8757,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8791,16 +8786,16 @@
         <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>212</v>
+        <v>447</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8907,7 +8902,7 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>450</v>
@@ -9237,7 +9232,7 @@
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9259,16 +9254,16 @@
         <v>111</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>212</v>
+        <v>447</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -10269,7 +10264,7 @@
         <v>503</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>21</v>
@@ -10303,7 +10298,7 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>505</v>
@@ -10631,7 +10626,7 @@
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10653,16 +10648,16 @@
         <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>212</v>
+        <v>447</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10886,7 +10881,7 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>522</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="550">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -639,24 +639,32 @@
     <t>MedicationRequest.contained</t>
   </si>
   <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
+    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung}
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
   </si>
   <si>
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>NewRx/MedicationPrescribed+-or-+RxFill/MedicationDispensed+-or-+RxHistoryResponse/MedicationDispensed+-or-+RxHistoryResponse/MedicationPrescribed</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct[classCode=ADMM]</t>
   </si>
   <si>
     <t>MedicationRequest.extension</t>
@@ -2071,14 +2079,14 @@
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.73046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="28.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="168.89453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4331,7 +4339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>199</v>
       </c>
@@ -4340,7 +4348,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4350,7 +4358,7 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
@@ -4359,16 +4367,16 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4418,7 +4426,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4436,10 +4444,10 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4450,10 +4458,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4482,7 +4490,7 @@
         <v>112</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>114</v>
@@ -4535,7 +4543,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4567,10 +4575,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4596,10 +4604,10 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4650,7 +4658,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4682,10 +4690,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4708,16 +4716,16 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4767,7 +4775,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4782,27 +4790,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4828,13 +4836,13 @@
         <v>166</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4863,10 +4871,10 @@
         <v>187</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4884,7 +4892,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>90</v>
@@ -4899,16 +4907,16 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>21</v>
@@ -4916,10 +4924,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4942,16 +4950,16 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4980,10 +4988,10 @@
         <v>156</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -5001,7 +5009,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5016,13 +5024,13 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
@@ -5033,10 +5041,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5062,13 +5070,13 @@
         <v>166</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5097,10 +5105,10 @@
         <v>187</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -5118,7 +5126,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5133,16 +5141,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>21</v>
@@ -5150,10 +5158,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5176,16 +5184,16 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5214,10 +5222,10 @@
         <v>156</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5235,7 +5243,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5253,13 +5261,13 @@
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>21</v>
@@ -5267,10 +5275,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5296,10 +5304,10 @@
         <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5329,10 +5337,10 @@
         <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5350,7 +5358,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5365,16 +5373,16 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>21</v>
@@ -5382,10 +5390,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5408,16 +5416,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5467,7 +5475,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5488,7 +5496,7 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
@@ -5499,10 +5507,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5525,13 +5533,13 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5582,7 +5590,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5603,7 +5611,7 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5614,10 +5622,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5640,16 +5648,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5678,10 +5686,10 @@
         <v>156</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5699,7 +5707,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>90</v>
@@ -5714,27 +5722,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5757,16 +5765,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5816,7 +5824,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -5831,27 +5839,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5874,16 +5882,16 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5933,7 +5941,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5948,27 +5956,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5991,13 +5999,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6048,7 +6056,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6063,16 +6071,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -6080,10 +6088,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6106,13 +6114,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6163,7 +6171,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6178,27 +6186,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6221,13 +6229,13 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6278,7 +6286,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6293,16 +6301,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6310,10 +6318,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6336,13 +6344,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6393,7 +6401,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6408,16 +6416,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6425,10 +6433,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6451,16 +6459,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6489,10 +6497,10 @@
         <v>156</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6510,7 +6518,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6525,13 +6533,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6542,10 +6550,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6568,13 +6576,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6625,7 +6633,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6646,10 +6654,10 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6657,10 +6665,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6683,16 +6691,16 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6721,10 +6729,10 @@
         <v>156</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6742,7 +6750,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6757,27 +6765,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6800,16 +6808,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6859,7 +6867,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6874,16 +6882,16 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6891,10 +6899,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6917,13 +6925,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6974,7 +6982,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6989,13 +6997,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -7006,10 +7014,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7035,10 +7043,10 @@
         <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7089,7 +7097,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7110,7 +7118,7 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7121,10 +7129,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7147,13 +7155,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7204,7 +7212,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7219,13 +7227,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7236,10 +7244,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7262,17 +7270,17 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7321,7 +7329,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7336,13 +7344,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7353,10 +7361,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7379,16 +7387,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7417,10 +7425,10 @@
         <v>156</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7438,7 +7446,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7459,7 +7467,7 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7470,10 +7478,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7496,13 +7504,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7553,7 +7561,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7568,13 +7576,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7585,10 +7593,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7611,13 +7619,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7668,7 +7676,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7683,13 +7691,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7700,10 +7708,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7726,16 +7734,16 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7773,17 +7781,17 @@
         <v>21</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7798,13 +7806,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7815,13 +7823,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>21</v>
@@ -7843,16 +7851,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7902,7 +7910,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7917,13 +7925,13 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7934,13 +7942,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>21</v>
@@ -7962,16 +7970,16 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8021,7 +8029,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8036,13 +8044,13 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8053,13 +8061,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>21</v>
@@ -8081,16 +8089,16 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8140,7 +8148,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8155,13 +8163,13 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8172,13 +8180,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>21</v>
@@ -8200,16 +8208,16 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8259,7 +8267,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8274,13 +8282,13 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8291,13 +8299,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>21</v>
@@ -8319,16 +8327,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8378,7 +8386,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8390,16 +8398,16 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8410,10 +8418,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8436,13 +8444,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8493,7 +8501,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8511,10 +8519,10 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8525,10 +8533,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8640,10 +8648,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8757,14 +8765,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8786,16 +8794,16 @@
         <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8844,7 +8852,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8876,10 +8884,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8902,16 +8910,16 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8961,7 +8969,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8982,7 +8990,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8993,10 +9001,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9108,10 +9116,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9225,14 +9233,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9254,16 +9262,16 @@
         <v>111</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9312,7 +9320,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9344,10 +9352,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9370,13 +9378,13 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9427,7 +9435,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9439,7 +9447,7 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -9448,7 +9456,7 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9459,10 +9467,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9485,13 +9493,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9542,7 +9550,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9563,7 +9571,7 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9574,10 +9582,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9600,13 +9608,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9657,7 +9665,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9678,7 +9686,7 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9689,10 +9697,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9715,19 +9723,19 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9776,7 +9784,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9794,10 +9802,10 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9808,10 +9816,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9834,16 +9842,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9893,7 +9901,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9911,24 +9919,24 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9951,13 +9959,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10008,7 +10016,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10020,30 +10028,30 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10066,16 +10074,16 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10125,7 +10133,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10143,10 +10151,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10157,10 +10165,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10183,13 +10191,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10240,7 +10248,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10261,10 +10269,10 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>21</v>
@@ -10272,10 +10280,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10298,13 +10306,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10355,7 +10363,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10373,10 +10381,10 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -10387,10 +10395,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10502,10 +10510,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10619,14 +10627,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10648,16 +10656,16 @@
         <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10706,7 +10714,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10738,10 +10746,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10764,16 +10772,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10802,10 +10810,10 @@
         <v>156</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -10823,7 +10831,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>90</v>
@@ -10841,24 +10849,24 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10881,13 +10889,13 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10917,10 +10925,10 @@
         <v>156</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -10938,7 +10946,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -10956,24 +10964,24 @@
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10996,13 +11004,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11053,7 +11061,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11068,13 +11076,13 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11085,14 +11093,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11111,16 +11119,16 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11170,7 +11178,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11191,7 +11199,7 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11202,10 +11210,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11228,16 +11236,16 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11287,7 +11295,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11302,13 +11310,13 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$76</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="541">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1328,7 +1328,7 @@
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension.value}
+    <t xml:space="preserve">value:extension.value.ofType(CodeableConcept).coding.code}
 </t>
   </si>
   <si>
@@ -1339,36 +1339,6 @@
   </si>
   <si>
     <t>see dosageInstruction mapping</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction:otherDosage</t>
-  </si>
-  <si>
-    <t>otherDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-other-administration}
-</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction:timedDosage</t>
-  </si>
-  <si>
-    <t>timedDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-timed-administration}
-</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction:frequencyDosage</t>
-  </si>
-  <si>
-    <t>frequencyDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-frequency-administration}
-</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction:freitextDosage</t>
@@ -2073,12 +2043,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO79"/>
+  <dimension ref="A1:AO76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.73046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="28.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2103,7 +2073,7 @@
     <col min="25" max="25" width="138.53125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="50.23046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -8041,7 +8011,7 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>426</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>418</v>
@@ -8059,16 +8029,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C52" t="s" s="2">
         <v>427</v>
       </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>21</v>
       </c>
@@ -8077,10 +8045,10 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
@@ -8092,14 +8060,12 @@
         <v>428</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8148,13 +8114,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -8163,13 +8129,13 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8178,16 +8144,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8196,10 +8160,10 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -8208,17 +8172,15 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>431</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>105</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8267,28 +8229,28 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>411</v>
+        <v>107</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>419</v>
+        <v>108</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8297,18 +8259,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8318,7 +8278,7 @@
         <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -8327,16 +8287,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>434</v>
+        <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>414</v>
+        <v>113</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>415</v>
+        <v>114</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8386,7 +8346,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>411</v>
+        <v>118</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8398,16 +8358,16 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>435</v>
+        <v>119</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>419</v>
+        <v>108</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8418,42 +8378,46 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>436</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8501,28 +8465,28 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>440</v>
+        <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>441</v>
+        <v>191</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8533,10 +8497,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8559,15 +8523,17 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>104</v>
+        <v>428</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>105</v>
+        <v>442</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8616,7 +8582,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>107</v>
+        <v>441</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8628,7 +8594,7 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -8637,7 +8603,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>108</v>
+        <v>445</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8648,21 +8614,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8674,17 +8640,15 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8733,19 +8697,19 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -8765,14 +8729,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>445</v>
+        <v>110</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8785,26 +8749,24 @@
         <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>446</v>
+        <v>112</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>447</v>
+        <v>113</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>448</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8852,7 +8814,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>449</v>
+        <v>118</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8873,7 +8835,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>191</v>
+        <v>108</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8884,44 +8846,46 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>436</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8969,19 +8933,19 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
@@ -8990,7 +8954,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>454</v>
+        <v>191</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -9001,10 +8965,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9027,13 +8991,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>104</v>
+        <v>450</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>105</v>
+        <v>451</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>106</v>
+        <v>452</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9084,7 +9048,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>107</v>
+        <v>449</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9096,7 +9060,7 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>21</v>
+        <v>453</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
@@ -9105,7 +9069,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>108</v>
+        <v>454</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9116,21 +9080,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -9142,17 +9106,15 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>111</v>
+        <v>456</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>112</v>
+        <v>457</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9201,19 +9163,19 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>118</v>
+        <v>455</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
@@ -9222,7 +9184,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>108</v>
+        <v>459</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9233,46 +9195,42 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>445</v>
+        <v>21</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>111</v>
+        <v>456</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9320,19 +9278,19 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
@@ -9341,7 +9299,7 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>191</v>
+        <v>459</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9352,10 +9310,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9378,16 +9336,20 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9435,7 +9397,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9447,16 +9409,16 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>462</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>21</v>
+        <v>469</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9467,10 +9429,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9493,15 +9455,17 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9550,7 +9514,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9568,24 +9532,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>21</v>
+        <v>476</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>21</v>
+        <v>478</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9608,13 +9572,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9665,7 +9629,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9677,30 +9641,30 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>453</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>21</v>
+        <v>482</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>21</v>
+        <v>484</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9723,20 +9687,18 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9784,7 +9746,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9802,10 +9764,10 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9816,10 +9778,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9842,17 +9804,15 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9901,7 +9861,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9919,24 +9879,24 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>485</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>487</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9959,13 +9919,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10016,7 +9976,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10028,30 +9988,30 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>462</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>493</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10074,17 +10034,15 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>465</v>
+        <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>495</v>
+        <v>105</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10133,7 +10091,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>494</v>
+        <v>107</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10145,16 +10103,16 @@
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>498</v>
+        <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>499</v>
+        <v>108</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10165,21 +10123,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -10191,15 +10149,17 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>501</v>
+        <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>502</v>
+        <v>112</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10248,19 +10208,19 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>500</v>
+        <v>118</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
@@ -10269,10 +10229,10 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>504</v>
+        <v>108</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>351</v>
+        <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>21</v>
@@ -10280,42 +10240,46 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>21</v>
+        <v>436</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L71" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10363,28 +10327,28 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>505</v>
+        <v>440</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>508</v>
+        <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>509</v>
+        <v>191</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -10395,10 +10359,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10406,7 +10370,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>90</v>
@@ -10421,15 +10385,17 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>104</v>
+        <v>505</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>105</v>
+        <v>506</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -10454,13 +10420,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>21</v>
+        <v>509</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>21</v>
+        <v>510</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -10478,10 +10444,10 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>107</v>
+        <v>504</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>90</v>
@@ -10490,41 +10456,41 @@
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>21</v>
+        <v>499</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>108</v>
+        <v>511</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>21</v>
+        <v>512</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
@@ -10536,17 +10502,15 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>111</v>
+        <v>235</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>112</v>
+        <v>514</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10571,13 +10535,13 @@
         <v>21</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>21</v>
+        <v>517</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -10595,78 +10559,74 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>118</v>
+        <v>513</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>21</v>
+        <v>518</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>108</v>
+        <v>519</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>21</v>
+        <v>520</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>445</v>
+        <v>21</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>111</v>
+        <v>522</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>446</v>
+        <v>523</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>21</v>
       </c>
@@ -10714,28 +10674,28 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>449</v>
+        <v>521</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>21</v>
+        <v>518</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>191</v>
+        <v>526</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10746,21 +10706,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>21</v>
+        <v>528</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10772,16 +10732,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10807,13 +10767,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>518</v>
+        <v>21</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>519</v>
+        <v>21</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -10831,13 +10791,13 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
@@ -10849,24 +10809,24 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>508</v>
+        <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>521</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10877,7 +10837,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10889,15 +10849,17 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>235</v>
+        <v>535</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10922,13 +10884,13 @@
         <v>21</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>525</v>
+        <v>21</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>526</v>
+        <v>21</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -10946,13 +10908,13 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
@@ -10961,372 +10923,23 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>21</v>
+        <v>539</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>527</v>
+        <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO79" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO79">
+  <autoFilter ref="A1:AO76">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11336,7 +10949,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI78">
+  <conditionalFormatting sqref="A2:AI75">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -643,7 +643,7 @@
 </t>
   </si>
   <si>
-    <t>TODO</t>
+    <t>Es sind nur die hier definierten contained Medication-Ressourcen zulässig. Contained (eingebettete) Ressourcen werden nicht separat versioniert, sondern ausschließlich im Rahmen der übergeordneten Ressource versioniert.</t>
   </si>
   <si>
     <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -639,7 +639,7 @@
     <t>MedicationRequest.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung}
+    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-wirkstoff}
 </t>
   </si>
   <si>
@@ -2056,7 +2056,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="168.89453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="237.0078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -568,7 +568,7 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
+    <t>Narrative - wird immer durch die Fachanwendung generiert.</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-base.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>At ELGA e-Medikation MedicationRequest Base</t>
+    <t>AT ELGA e-Medikation MedicationRequest Base</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
